--- a/DataMapping.xlsx
+++ b/DataMapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apier\PycharmProjects\SATS+\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680278EE-EE61-4D8F-9043-C4A791BDD713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541DAE8C-45F2-46DE-B1EE-8191E54C7B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14940" yWindow="-16308" windowWidth="29016" windowHeight="15696" xr2:uid="{9EBCAD18-D0E1-4DCE-95F9-AB28646FE52F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9EBCAD18-D0E1-4DCE-95F9-AB28646FE52F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="256">
   <si>
     <t>HIDE Help</t>
   </si>
@@ -762,13 +762,58 @@
   </si>
   <si>
     <t>Q278_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q569_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q570_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q571_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q572_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q573_Lr{N}</t>
+  </si>
+  <si>
+    <t>qPriceTransparency</t>
+  </si>
+  <si>
+    <t>qExperienceCost</t>
+  </si>
+  <si>
+    <t>qLocalsValue</t>
+  </si>
+  <si>
+    <t>qValueComparison</t>
+  </si>
+  <si>
+    <t>qValueAligment</t>
+  </si>
+  <si>
+    <t>Q556_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q557_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q560_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q559_Lr{N}</t>
+  </si>
+  <si>
+    <t>Q558_Lr{N}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -798,13 +843,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -870,12 +908,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1663,300 +1700,300 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+    <row r="44" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+    <row r="45" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+    <row r="47" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+    <row r="48" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+    <row r="49" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
+    <row r="50" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
+    <row r="51" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
+    <row r="52" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
+    <row r="53" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
+    <row r="54" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
+    <row r="55" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
+    <row r="56" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
+    <row r="57" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
+    <row r="58" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
+    <row r="59" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
+    <row r="60" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
+    <row r="61" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
+    <row r="62" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
+    <row r="63" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
+    <row r="64" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
+    <row r="65" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
+    <row r="66" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
+    <row r="67" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="6" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2103,146 +2140,146 @@
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
+    <row r="81" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
+    <row r="82" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
+    <row r="83" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
+    <row r="84" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
+    <row r="85" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
+    <row r="86" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
+    <row r="87" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
+    <row r="88" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
+    <row r="89" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
+    <row r="90" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
+    <row r="91" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
+    <row r="92" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
+    <row r="93" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="6" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2279,29 +2316,69 @@
         <v>221</v>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C97" s="4"/>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C98" s="5"/>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C99" s="5"/>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C100" s="5"/>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C101" s="5"/>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C102" s="5"/>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C103" s="5"/>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C104" s="5"/>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>251</v>
+      </c>
+      <c r="B97" t="s">
+        <v>241</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>252</v>
+      </c>
+      <c r="B98" t="s">
+        <v>242</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>253</v>
+      </c>
+      <c r="B99" t="s">
+        <v>243</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>254</v>
+      </c>
+      <c r="B100" t="s">
+        <v>244</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>255</v>
+      </c>
+      <c r="B101" t="s">
+        <v>245</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C102" s="4"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C103" s="4"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C104" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
